--- a/TestCase/CABSystem_TestCases (2).xlsx
+++ b/TestCase/CABSystem_TestCases (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120" firstSheet="4" activeTab="7"/>
+    <workbookView windowWidth="11520" windowHeight="9120" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Mô tả các cột" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="Rating Test Cases" sheetId="6" r:id="rId6"/>
     <sheet name="Notification Tests" sheetId="7" r:id="rId7"/>
     <sheet name="Operations Tests" sheetId="8" r:id="rId8"/>
+    <sheet name="Login Test Cases" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="915">
   <si>
     <t>Cột</t>
   </si>
@@ -3178,6 +3179,371 @@
   <si>
     <t>Dữ liệu được cập nhật đúng; trường không được phép không thay đổi; có audit log
 FR/UC: FR32; AC09.4; NFR15</t>
+  </si>
+  <si>
+    <t>TC-AUTH-001</t>
+  </si>
+  <si>
+    <t>Người dùng đăng nhập</t>
+  </si>
+  <si>
+    <t>Đăng nhập với username và password hợp lệ</t>
+  </si>
+  <si>
+    <t>Tài khoản đã đăng ký và đang Active</t>
+  </si>
+  <si>
+    <t>1. Mở Login
+2. Nhập username
+3. Nhập password
+4. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công; tạo phiên/token và chuyển vào hệ thống</t>
+  </si>
+  <si>
+    <t>TC-AUTH-002</t>
+  </si>
+  <si>
+    <t>Đăng nhập với username không tồn tại</t>
+  </si>
+  <si>
+    <t>Username: unknown01
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại; hiển thị thông báo thông tin đăng nhập không hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-003</t>
+  </si>
+  <si>
+    <t>Đăng nhập với password không đúng</t>
+  </si>
+  <si>
+    <t>Username tồn tại và tài khoản Active</t>
+  </si>
+  <si>
+    <t>1. Mở Login
+2. Nhập username đúng
+3. Nhập password sai
+4. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: Wrong@123</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại; không tạo phiên/token</t>
+  </si>
+  <si>
+    <t>TC-AUTH-004</t>
+  </si>
+  <si>
+    <t>Username để trống</t>
+  </si>
+  <si>
+    <t>Đang ở màn hình Login</t>
+  </si>
+  <si>
+    <t>1. Để trống username
+2. Nhập password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: empty
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Không cho đăng nhập; hiển thị lỗi yêu cầu nhập username</t>
+  </si>
+  <si>
+    <t>TC-AUTH-005</t>
+  </si>
+  <si>
+    <t>Password để trống</t>
+  </si>
+  <si>
+    <t>1. Nhập username
+2. Để trống password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: empty</t>
+  </si>
+  <si>
+    <t>Không cho đăng nhập; hiển thị lỗi yêu cầu nhập password</t>
+  </si>
+  <si>
+    <t>TC-AUTH-006</t>
+  </si>
+  <si>
+    <t>Username và password đều để trống</t>
+  </si>
+  <si>
+    <t>1. Không nhập username
+2. Không nhập password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: empty
+Password: empty</t>
+  </si>
+  <si>
+    <t>Không cho đăng nhập; hiển thị lỗi validation tương ứng</t>
+  </si>
+  <si>
+    <t>TC-AUTH-007</t>
+  </si>
+  <si>
+    <t>Username có định dạng không hợp lệ</t>
+  </si>
+  <si>
+    <t>1. Nhập username không hợp lệ
+2. Nhập password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user@@@
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Từ chối dữ liệu và hiển thị lỗi username không hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-008</t>
+  </si>
+  <si>
+    <t>Password có định dạng không hợp lệ</t>
+  </si>
+  <si>
+    <t>Quy tắc password đã được định nghĩa</t>
+  </si>
+  <si>
+    <t>1. Nhập username
+2. Nhập password không đáp ứng rule
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: 123</t>
+  </si>
+  <si>
+    <t>Từ chối dữ liệu và hiển thị lỗi password không hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-009</t>
+  </si>
+  <si>
+    <t>Đăng nhập bằng tài khoản bị khóa</t>
+  </si>
+  <si>
+    <t>Tài khoản user01 ở trạng thái Locked</t>
+  </si>
+  <si>
+    <t>1. Nhập username
+2. Nhập password đúng
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại; thông báo tài khoản bị khóa</t>
+  </si>
+  <si>
+    <t>TC-AUTH-010</t>
+  </si>
+  <si>
+    <t>Đăng nhập bằng tài khoản Inactive</t>
+  </si>
+  <si>
+    <t>Tài khoản tồn tại nhưng Inactive</t>
+  </si>
+  <si>
+    <t>Username: inactive01
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại; thông báo tài khoản không hoạt động</t>
+  </si>
+  <si>
+    <t>TC-AUTH-011</t>
+  </si>
+  <si>
+    <t>Username phân biệt chữ hoa/chữ thường</t>
+  </si>
+  <si>
+    <t>Quy tắc xử lý username đã xác định</t>
+  </si>
+  <si>
+    <t>1. Nhập username khác hoa/thường
+2. Nhập password đúng
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: User01
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Xử lý đúng theo rule case-sensitive/case-insensitive</t>
+  </si>
+  <si>
+    <t>TC-AUTH-012</t>
+  </si>
+  <si>
+    <t>Password phân biệt chữ hoa/chữ thường</t>
+  </si>
+  <si>
+    <t>Tài khoản Active</t>
+  </si>
+  <si>
+    <t>1. Nhập username đúng
+2. Nhập password khác hoa/thường
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: password@123</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại nếu password phân biệt hoa/thường</t>
+  </si>
+  <si>
+    <t>TC-AUTH-013</t>
+  </si>
+  <si>
+    <t>Nhập password chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>1. Nhập username
+2. Nhập password có khoảng trắng
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username: user01
+Password:  Password@123 </t>
+  </si>
+  <si>
+    <t>Xử lý khoảng trắng đúng theo Business Rule</t>
+  </si>
+  <si>
+    <t>TC-AUTH-014</t>
+  </si>
+  <si>
+    <t>Kiểm tra password không hiển thị plaintext</t>
+  </si>
+  <si>
+    <t>1. Click ô Password
+2. Nhập password</t>
+  </si>
+  <si>
+    <t>Password: Password@123</t>
+  </si>
+  <si>
+    <t>Password được che/mask</t>
+  </si>
+  <si>
+    <t>TC-AUTH-015</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công và truy cập chức năng được phép</t>
+  </si>
+  <si>
+    <t>Tài khoản Active và có quyền</t>
+  </si>
+  <si>
+    <t>1. Nhập username hợp lệ
+2. Nhập password hợp lệ
+3. Login
+4. Truy cập chức năng yêu cầu authentication</t>
+  </si>
+  <si>
+    <t>Authentication thành công và truy cập được chức năng được cấp quyền</t>
+  </si>
+  <si>
+    <t>TC-AUTH-016</t>
+  </si>
+  <si>
+    <t>Đăng nhập nhiều lần với password sai</t>
+  </si>
+  <si>
+    <t>Có cơ chế giới hạn số lần đăng nhập sai</t>
+  </si>
+  <si>
+    <t>1. Nhập username đúng
+2. Nhập password sai
+3. Lặp lại theo số lần quy định</t>
+  </si>
+  <si>
+    <t>Sau số lần sai theo Business Rule, tài khoản bị khóa hoặc áp dụng cơ chế bảo vệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-017</t>
+  </si>
+  <si>
+    <t>Request không có username</t>
+  </si>
+  <si>
+    <t>API Login đang hoạt động</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login
+2. Bỏ trường username</t>
+  </si>
+  <si>
+    <t>{ password: Password@123 }</t>
+  </si>
+  <si>
+    <t>API trả lỗi validation; không authentication</t>
+  </si>
+  <si>
+    <t>TC-AUTH-018</t>
+  </si>
+  <si>
+    <t>Request không có password</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login
+2. Bỏ trường password</t>
+  </si>
+  <si>
+    <t>{ username: user01 }</t>
+  </si>
+  <si>
+    <t>TC-AUTH-019</t>
+  </si>
+  <si>
+    <t>Request với username/password không hợp lệ</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login
+2. Nhập dữ liệu không hợp lệ</t>
+  </si>
+  <si>
+    <t>Username: unknown
+Password: wrong</t>
+  </si>
+  <si>
+    <t>API trả response lỗi phù hợp; không tạo token</t>
+  </si>
+  <si>
+    <t>TC-AUTH-020</t>
+  </si>
+  <si>
+    <t>Response không trả về password</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login hợp lệ
+2. Kiểm tra response</t>
+  </si>
+  <si>
+    <t>Response không chứa password hoặc thông tin nhạy cảm</t>
   </si>
 </sst>
 </file>
@@ -3190,11 +3556,26 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3674,28 +4055,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3704,139 +4076,154 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4466,128 +4853,128 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1" spans="1:4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1" spans="1:4">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4617,522 +5004,522 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" ht="76" customHeight="1" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" ht="76" customHeight="1" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" ht="76" customHeight="1" spans="1:8">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" ht="76" customHeight="1" spans="1:8">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1" spans="1:8">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5175,1276 +5562,1276 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" ht="76" customHeight="1" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" ht="76" customHeight="1" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" ht="76" customHeight="1" spans="1:8">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" ht="76" customHeight="1" spans="1:8">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1" spans="1:8">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1" spans="1:8">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" ht="76" customHeight="1" spans="1:8">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1" spans="1:8">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="24" ht="76" customHeight="1" spans="1:8">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="25" ht="76" customHeight="1" spans="1:8">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" ht="76" customHeight="1" spans="1:8">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="27" ht="76" customHeight="1" spans="1:8">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" ht="76" customHeight="1" spans="1:8">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="29" ht="76" customHeight="1" spans="1:8">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" ht="76" customHeight="1" spans="1:8">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="31" ht="76" customHeight="1" spans="1:8">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="32" ht="76" customHeight="1" spans="1:8">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="33" ht="76" customHeight="1" spans="1:8">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="34" ht="76" customHeight="1" spans="1:8">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" ht="76" customHeight="1" spans="1:8">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="36" ht="76" customHeight="1" spans="1:8">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="37" ht="78" customHeight="1" spans="1:8">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1" spans="1:8">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1" spans="1:8">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1" spans="1:8">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1" spans="1:8">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="42" ht="78" customHeight="1" spans="1:8">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1" spans="1:8">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" ht="78" customHeight="1" spans="1:8">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" ht="78" customHeight="1" spans="1:8">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="46" ht="78" customHeight="1" spans="1:8">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="47" ht="78" customHeight="1" spans="1:8">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="48" ht="78" customHeight="1" spans="1:8">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="49" ht="78" customHeight="1" spans="1:8">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="5" t="s">
         <v>65</v>
       </c>
     </row>
@@ -6487,392 +6874,392 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" ht="76" customHeight="1" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1" spans="1:8">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -6915,496 +7302,496 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="14" ht="76" customHeight="1" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" ht="76" customHeight="1" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1" spans="1:8">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1" spans="1:8">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="5" t="s">
         <v>65</v>
       </c>
     </row>
@@ -7447,340 +7834,340 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7823,366 +8210,366 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:8">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>656</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>657</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="6" t="s">
         <v>658</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:8">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>662</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>664</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>665</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:8">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>672</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="6" t="s">
         <v>673</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:8">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:8">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>688</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1" spans="1:8">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>694</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1" spans="1:8">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>698</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>699</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="6" t="s">
         <v>700</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>702</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1" spans="1:8">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>704</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>705</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>708</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>709</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>65</v>
       </c>
     </row>
@@ -8225,496 +8612,496 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1" spans="1:8">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>762</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>763</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>766</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1" spans="1:8">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>769</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="6" t="s">
         <v>770</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>772</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1" spans="1:8">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>774</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>778</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1" spans="1:8">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="6" t="s">
         <v>782</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>783</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" ht="78" customHeight="1" spans="1:8">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>787</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>788</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>790</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" ht="78" customHeight="1" spans="1:8">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>791</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="6" t="s">
         <v>794</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1" spans="1:8">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="6" t="s">
         <v>800</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1" spans="1:8">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="6" t="s">
         <v>806</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>808</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8738,4 +9125,562 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" ht="28.8" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" ht="115.2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" ht="115.2" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" ht="144" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" ht="86.4" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" ht="86.4" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" ht="115.2" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="115.2" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" ht="115.2" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" ht="100.8" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" ht="100.8" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" ht="144" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="144" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="115.2" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="72" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="172.8" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" ht="129.6" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" ht="86.4" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" ht="86.4" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" ht="86.4" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" ht="100.8" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>